--- a/CodeVS/data/output/cost_schedule_Export_test.xlsx
+++ b/CodeVS/data/output/cost_schedule_Export_test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="90">
   <si>
     <t>TugboatId</t>
   </si>
@@ -85,66 +85,78 @@
     <t>RiverTB_06</t>
   </si>
   <si>
+    <t>RiverTB_09</t>
+  </si>
+  <si>
+    <t>RiverTB_10</t>
+  </si>
+  <si>
+    <t>RiverTB_13</t>
+  </si>
+  <si>
+    <t>SeaTB_02</t>
+  </si>
+  <si>
+    <t>SeaTB_03</t>
+  </si>
+  <si>
+    <t>SeaTB_06</t>
+  </si>
+  <si>
+    <t>SeaTB_07</t>
+  </si>
+  <si>
+    <t>SeaTB_08</t>
+  </si>
+  <si>
+    <t>SeaTB_09</t>
+  </si>
+  <si>
+    <t>SeaTB_11</t>
+  </si>
+  <si>
+    <t>SeaTB_12</t>
+  </si>
+  <si>
     <t>RiverTB_08</t>
   </si>
   <si>
     <t>RiverTB_11</t>
   </si>
   <si>
-    <t>RiverTB_13</t>
-  </si>
-  <si>
-    <t>SeaTB_02</t>
-  </si>
-  <si>
-    <t>SeaTB_03</t>
+    <t>RiverTB_12</t>
   </si>
   <si>
     <t>SeaTB_04</t>
   </si>
   <si>
-    <t>SeaTB_07</t>
-  </si>
-  <si>
-    <t>SeaTB_08</t>
-  </si>
-  <si>
-    <t>SeaTB_11</t>
-  </si>
-  <si>
-    <t>SeaTB_12</t>
-  </si>
-  <si>
-    <t>RiverTB_12</t>
-  </si>
-  <si>
-    <t>RiverTB_09</t>
-  </si>
-  <si>
-    <t>RiverTB_10</t>
-  </si>
-  <si>
-    <t>SeaTB_06</t>
-  </si>
-  <si>
-    <t>SeaTB_09</t>
-  </si>
-  <si>
     <t>Order_50</t>
   </si>
   <si>
-    <t>Order_50, Order_51</t>
-  </si>
-  <si>
     <t>Order_51</t>
   </si>
   <si>
+    <t>Order_51, Order_50</t>
+  </si>
+  <si>
     <t>Order_52</t>
   </si>
   <si>
+    <t>ST_045</t>
+  </si>
+  <si>
     <t>ST_014</t>
   </si>
   <si>
+    <t>ST_049</t>
+  </si>
+  <si>
+    <t>Collecting Barge - B_081 - (ST_001 to ST_001)</t>
+  </si>
+  <si>
+    <t>Collecting Barge - B_015 - (ST_001 to ST_001)</t>
+  </si>
+  <si>
     <t>ST_001</t>
   </si>
   <si>
@@ -154,36 +166,24 @@
     <t>Collecting Barge - B_075 - (ST_014 to ST_001)</t>
   </si>
   <si>
-    <t>ST_045</t>
-  </si>
-  <si>
     <t>ST_050</t>
   </si>
   <si>
-    <t>ST_049</t>
-  </si>
-  <si>
-    <t>Collecting Barge - B_083 - (ST_001 to ST_001)</t>
-  </si>
-  <si>
-    <t>Collecting Barge - B_015 - (ST_001 to ST_001)</t>
-  </si>
-  <si>
     <t>Start Collect Barge River Down From ST_014 To ST_014</t>
   </si>
   <si>
+    <t>ST_013</t>
+  </si>
+  <si>
+    <t>B_047)</t>
+  </si>
+  <si>
     <t>B_016)</t>
   </si>
   <si>
     <t>B_098)</t>
   </si>
   <si>
-    <t>ST_013</t>
-  </si>
-  <si>
-    <t>B_050)</t>
-  </si>
-  <si>
     <t>ST_044</t>
   </si>
   <si>
@@ -196,7 +196,40 @@
     <t>Travel To Carrier</t>
   </si>
   <si>
-    <t>B_033, B_017, B_024</t>
+    <t>B_090, B_010, B_100</t>
+  </si>
+  <si>
+    <t>B_081, B_047, B_101, B_085</t>
+  </si>
+  <si>
+    <t>B_095, B_088</t>
+  </si>
+  <si>
+    <t>B_026, B_064, B_030</t>
+  </si>
+  <si>
+    <t>B_087, B_046, B_061, B_059</t>
+  </si>
+  <si>
+    <t>B_042, B_058, B_045, B_040</t>
+  </si>
+  <si>
+    <t>B_041, B_013</t>
+  </si>
+  <si>
+    <t>B_040, B_087, B_046, B_061</t>
+  </si>
+  <si>
+    <t>B_088, B_026, B_064, B_030</t>
+  </si>
+  <si>
+    <t>B_015, B_019, B_042, B_058, B_045</t>
+  </si>
+  <si>
+    <t>B_059, B_090, B_010, B_100, B_095</t>
+  </si>
+  <si>
+    <t>B_081, B_047</t>
   </si>
   <si>
     <t>B_032, B_008, B_048</t>
@@ -211,6 +244,9 @@
     <t>B_043, B_076, B_077, B_055</t>
   </si>
   <si>
+    <t>B_033, B_017, B_024, B_016</t>
+  </si>
+  <si>
     <t>B_060, B_082, B_038, B_091</t>
   </si>
   <si>
@@ -232,58 +268,22 @@
     <t>B_069, B_098, B_015, B_019</t>
   </si>
   <si>
-    <t>B_016, B_083, B_050, B_102, B_085</t>
-  </si>
-  <si>
-    <t>B_033, B_017, B_024, B_016, B_102, B_085</t>
-  </si>
-  <si>
-    <t>B_090, B_010, B_100</t>
-  </si>
-  <si>
-    <t>B_095, B_088</t>
-  </si>
-  <si>
-    <t>B_026, B_064, B_030</t>
-  </si>
-  <si>
-    <t>B_087, B_046, B_061, B_059</t>
-  </si>
-  <si>
-    <t>B_042, B_058, B_045, B_040</t>
-  </si>
-  <si>
-    <t>B_041, B_013</t>
-  </si>
-  <si>
-    <t>B_040, B_087, B_046, B_061</t>
-  </si>
-  <si>
-    <t>B_088, B_026, B_064, B_030</t>
-  </si>
-  <si>
-    <t>B_015, B_019, B_042, B_058, B_045</t>
-  </si>
-  <si>
-    <t>B_059, B_090, B_010, B_100, B_095</t>
-  </si>
-  <si>
-    <t>B_083, B_050</t>
-  </si>
-  <si>
-    <t>B_028, B_081, B_020</t>
-  </si>
-  <si>
-    <t>B_068, B_027, B_097, B_023</t>
-  </si>
-  <si>
-    <t>B_005, B_006, B_003, B_004, B_019, B_015</t>
-  </si>
-  <si>
-    <t>B_067, B_056, B_049, B_101, B_062</t>
-  </si>
-  <si>
-    <t>B_022, B_093, B_034</t>
+    <t>B_033, B_017, B_024, B_016, B_101, B_085</t>
+  </si>
+  <si>
+    <t>B_068, B_083, B_020</t>
+  </si>
+  <si>
+    <t>B_027, B_099, B_023, B_028</t>
+  </si>
+  <si>
+    <t>B_005, B_006, B_003, B_004, B_067, B_049</t>
+  </si>
+  <si>
+    <t>B_019, B_015, B_102, B_063, B_071</t>
+  </si>
+  <si>
+    <t>B_022, B_094</t>
   </si>
 </sst>
 </file>
@@ -645,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:T53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -730,22 +730,22 @@
         <v>0.3</v>
       </c>
       <c r="G2">
-        <v>8150</v>
+        <v>7700</v>
       </c>
       <c r="H2" s="2">
-        <v>45988.29166666666</v>
+        <v>45983.86458333334</v>
       </c>
       <c r="I2" s="2">
-        <v>45988.29166666666</v>
+        <v>45985.01041666666</v>
       </c>
       <c r="J2" s="2">
-        <v>45989.41390423573</v>
+        <v>45986.13427084097</v>
       </c>
       <c r="K2" t="s">
         <v>42</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N2">
         <v>1.5</v>
@@ -754,13 +754,13 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>11.08333333333333</v>
       </c>
       <c r="Q2">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="R2">
-        <v>26.9337016575</v>
+        <v>54.47250018333333</v>
       </c>
       <c r="S2" t="s">
         <v>57</v>
@@ -771,7 +771,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
         <v>38</v>
@@ -789,25 +789,25 @@
         <v>0.3</v>
       </c>
       <c r="G3">
-        <v>6950</v>
+        <v>8200</v>
       </c>
       <c r="H3" s="2">
-        <v>45984.95833333334</v>
+        <v>45993.01041666666</v>
       </c>
       <c r="I3" s="2">
-        <v>45985</v>
+        <v>45993.01041666666</v>
       </c>
       <c r="J3" s="2">
-        <v>45986.11822543956</v>
+        <v>45994.38510101011</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -816,10 +816,10 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="R3">
-        <v>27.83741054944445</v>
+        <v>32.9924242425</v>
       </c>
       <c r="S3" t="s">
         <v>57</v>
@@ -830,7 +830,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>38</v>
@@ -848,37 +848,37 @@
         <v>0.3</v>
       </c>
       <c r="G4">
-        <v>7000</v>
+        <v>6300</v>
       </c>
       <c r="H4" s="2">
-        <v>45984.86458333334</v>
+        <v>45986.11458333334</v>
       </c>
       <c r="I4" s="2">
-        <v>45984.90625</v>
+        <v>45986.61458333334</v>
       </c>
       <c r="J4" s="2">
-        <v>45985.99060296014</v>
+        <v>45987.50375139587</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R4">
-        <v>27.02447104333333</v>
+        <v>33.34003350083334</v>
       </c>
       <c r="S4" t="s">
         <v>57</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
         <v>38</v>
@@ -907,22 +907,22 @@
         <v>0.3</v>
       </c>
       <c r="G5">
-        <v>7500</v>
+        <v>8100</v>
       </c>
       <c r="H5" s="2">
-        <v>45984.78125</v>
+        <v>45985.98958333334</v>
       </c>
       <c r="I5" s="2">
-        <v>45984.82291666666</v>
+        <v>45986.48958333334</v>
       </c>
       <c r="J5" s="2">
-        <v>45986.02323661984</v>
+        <v>45987.60901629935</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N5">
         <v>1.5</v>
@@ -931,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5">
-        <v>29.80767887611111</v>
+        <v>38.86639118444445</v>
       </c>
       <c r="S5" t="s">
         <v>57</v>
@@ -948,7 +948,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
         <v>38</v>
@@ -966,22 +966,22 @@
         <v>0.3</v>
       </c>
       <c r="G6">
-        <v>12000</v>
+        <v>10050</v>
       </c>
       <c r="H6" s="2">
-        <v>45984.84375</v>
+        <v>45984.94791666666</v>
       </c>
       <c r="I6" s="2">
-        <v>45984.90625</v>
+        <v>45985.01041666666</v>
       </c>
       <c r="J6" s="2">
-        <v>45986.20849215214</v>
+        <v>45986.18867476596</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6">
         <v>2</v>
@@ -996,7 +996,7 @@
         <v>2</v>
       </c>
       <c r="R6">
-        <v>32.75381165138889</v>
+        <v>29.77819438305556</v>
       </c>
       <c r="S6" t="s">
         <v>57</v>
@@ -1007,7 +1007,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
         <v>38</v>
@@ -1025,22 +1025,22 @@
         <v>0.3</v>
       </c>
       <c r="G7">
-        <v>11650</v>
+        <v>9750</v>
       </c>
       <c r="H7" s="2">
-        <v>45984.9375</v>
+        <v>45984.92708333334</v>
       </c>
       <c r="I7" s="2">
-        <v>45985</v>
+        <v>45984.98958333334</v>
       </c>
       <c r="J7" s="2">
-        <v>45986.27906395431</v>
+        <v>45986.21342477692</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N7">
         <v>2</v>
@@ -1055,7 +1055,7 @@
         <v>2</v>
       </c>
       <c r="R7">
-        <v>32.19753490333333</v>
+        <v>30.87219464611111</v>
       </c>
       <c r="S7" t="s">
         <v>57</v>
@@ -1066,58 +1066,58 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
       </c>
       <c r="C8">
-        <v>9.334371213944859</v>
+        <v>0.01</v>
       </c>
       <c r="D8">
-        <v>62.21893992770459</v>
+        <v>145</v>
       </c>
       <c r="E8">
         <v>30</v>
       </c>
       <c r="F8">
-        <v>280.0311364183458</v>
+        <v>0.3</v>
       </c>
       <c r="G8">
-        <v>7750</v>
+        <v>5600</v>
       </c>
       <c r="H8" s="2">
-        <v>45983.95833333334</v>
+        <v>45986.28125</v>
+      </c>
+      <c r="I8" s="2">
+        <v>45986.78125</v>
       </c>
       <c r="J8" s="2">
-        <v>45984.84726546724</v>
+        <v>45987.54752008867</v>
       </c>
       <c r="K8" t="s">
-        <v>42</v>
-      </c>
-      <c r="L8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N8">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8">
-        <v>21.33437121388889</v>
+        <v>30.39048212805556</v>
       </c>
       <c r="S8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T8" t="s">
         <v>66</v>
@@ -1125,43 +1125,40 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
         <v>38</v>
       </c>
       <c r="C9">
-        <v>9.110310455088765</v>
+        <v>7.559549950030005</v>
       </c>
       <c r="D9">
         <v>62.21893992770459</v>
       </c>
       <c r="E9">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>592.1701795807697</v>
+        <v>226.7864985009002</v>
       </c>
       <c r="G9">
-        <v>7250</v>
+        <v>5600</v>
       </c>
       <c r="H9" s="2">
-        <v>45984.35416666666</v>
+        <v>45984.85416666666</v>
       </c>
       <c r="J9" s="2">
-        <v>45984.83792960229</v>
+        <v>45985.45734235903</v>
       </c>
       <c r="K9" t="s">
         <v>43</v>
       </c>
-      <c r="L9" t="s">
-        <v>43</v>
-      </c>
       <c r="M9" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="N9">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1170,57 +1167,57 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9">
-        <v>11.610310455</v>
+        <v>14.47621661666667</v>
       </c>
       <c r="S9" t="s">
         <v>58</v>
       </c>
       <c r="T9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
       </c>
       <c r="C10">
-        <v>10.79467394230661</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>62.21893992770459</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F10">
-        <v>323.8402182691982</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2">
         <v>45983.95833333334</v>
       </c>
       <c r="J10" s="2">
-        <v>45984.93241696982</v>
+        <v>45984.40972222222</v>
       </c>
       <c r="K10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L10" t="s">
         <v>43</v>
       </c>
       <c r="M10" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1232,24 +1229,18 @@
         <v>2</v>
       </c>
       <c r="R10">
-        <v>23.37800727555555</v>
-      </c>
-      <c r="S10" t="s">
-        <v>58</v>
-      </c>
-      <c r="T10" t="s">
-        <v>68</v>
+        <v>10.83333333333333</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
       </c>
       <c r="C11">
-        <v>11.35842716732944</v>
+        <v>10.70374352527781</v>
       </c>
       <c r="D11">
         <v>62.21893992770459</v>
@@ -1258,28 +1249,25 @@
         <v>65</v>
       </c>
       <c r="F11">
-        <v>738.2977658764135</v>
+        <v>695.7433291430575</v>
       </c>
       <c r="G11">
-        <v>12350</v>
+        <v>10050</v>
       </c>
       <c r="H11" s="2">
-        <v>45984.375</v>
+        <v>45982.71908524904</v>
       </c>
       <c r="J11" s="2">
-        <v>45985.02187890975</v>
+        <v>45983.52271345148</v>
       </c>
       <c r="K11" t="s">
         <v>43</v>
       </c>
-      <c r="L11" t="s">
-        <v>43</v>
-      </c>
       <c r="M11" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="N11">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1291,42 +1279,42 @@
         <v>2</v>
       </c>
       <c r="R11">
-        <v>15.52509383388889</v>
+        <v>19.28707685861111</v>
       </c>
       <c r="S11" t="s">
         <v>58</v>
       </c>
       <c r="T11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
         <v>38</v>
       </c>
       <c r="C12">
-        <v>9.967111735991512</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>62.21893992770459</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>65</v>
       </c>
       <c r="F12">
-        <v>647.8622628394482</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2">
-        <v>45984.375</v>
+        <v>45983.94791666666</v>
       </c>
       <c r="J12" s="2">
-        <v>45984.92918521123</v>
+        <v>45984.39930555555</v>
       </c>
       <c r="K12" t="s">
         <v>43</v>
@@ -1335,10 +1323,10 @@
         <v>43</v>
       </c>
       <c r="M12" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -1350,13 +1338,7 @@
         <v>2</v>
       </c>
       <c r="R12">
-        <v>13.30044506944444</v>
-      </c>
-      <c r="S12" t="s">
-        <v>58</v>
-      </c>
-      <c r="T12" t="s">
-        <v>70</v>
+        <v>10.83333333333333</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1382,16 +1364,19 @@
         <v>0</v>
       </c>
       <c r="H13" s="2">
-        <v>45984.9375</v>
+        <v>45983.94791666666</v>
       </c>
       <c r="J13" s="2">
-        <v>45990.23958333334</v>
+        <v>45984.39930555555</v>
       </c>
       <c r="K13" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="L13" t="s">
+        <v>43</v>
       </c>
       <c r="M13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -1403,15 +1388,15 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="R13">
-        <v>127.25</v>
+        <v>10.83333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
         <v>38</v>
@@ -1432,10 +1417,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2">
-        <v>45983.94791666666</v>
+        <v>45985.21180555555</v>
       </c>
       <c r="J14" s="2">
-        <v>45988</v>
+        <v>45985.36458333334</v>
       </c>
       <c r="K14" t="s">
         <v>45</v>
@@ -1453,51 +1438,48 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="R14">
-        <v>97.25</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
         <v>38</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>9.702185552813946</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>62.21893992770459</v>
       </c>
       <c r="E15">
         <v>65</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>630.6420609329065</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>11250</v>
       </c>
       <c r="H15" s="2">
-        <v>45983.94791666666</v>
+        <v>45982.71908524904</v>
       </c>
       <c r="J15" s="2">
-        <v>45984.39930555555</v>
+        <v>45983.4809818693</v>
       </c>
       <c r="K15" t="s">
-        <v>42</v>
-      </c>
-      <c r="L15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M15" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -1509,48 +1491,54 @@
         <v>2</v>
       </c>
       <c r="R15">
-        <v>10.83333333333333</v>
+        <v>18.28551888611111</v>
+      </c>
+      <c r="S15" t="s">
+        <v>58</v>
+      </c>
+      <c r="T15" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16">
-        <v>0.01</v>
+        <v>11.11052498709011</v>
       </c>
       <c r="D16">
-        <v>144</v>
+        <v>62.21893992770459</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F16">
-        <v>0.3</v>
+        <v>722.1841241608569</v>
       </c>
       <c r="G16">
-        <v>9550</v>
+        <v>11800</v>
       </c>
       <c r="H16" s="2">
-        <v>45984.92708333334</v>
-      </c>
-      <c r="I16" s="2">
-        <v>45984.98958333334</v>
+        <v>45984.20833333334</v>
       </c>
       <c r="J16" s="2">
-        <v>45986.09673218481</v>
+        <v>45985.01154965225</v>
       </c>
       <c r="K16" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="L16" t="s">
+        <v>47</v>
       </c>
       <c r="M16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N16">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -1562,51 +1550,51 @@
         <v>2</v>
       </c>
       <c r="R16">
-        <v>28.07157243555556</v>
+        <v>19.27719165388889</v>
       </c>
       <c r="S16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17">
-        <v>0.01</v>
+        <v>11.71486316630421</v>
       </c>
       <c r="D17">
-        <v>144</v>
+        <v>62.21893992770459</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F17">
-        <v>0.3</v>
+        <v>761.4661058097738</v>
       </c>
       <c r="G17">
-        <v>9700</v>
+        <v>13100</v>
       </c>
       <c r="H17" s="2">
-        <v>45989.83333333334</v>
-      </c>
-      <c r="I17" s="2">
-        <v>45989.83333333334</v>
+        <v>45984.375</v>
       </c>
       <c r="J17" s="2">
-        <v>45991.16837712096</v>
+        <v>45985.03673040971</v>
       </c>
       <c r="K17" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="L17" t="s">
+        <v>47</v>
       </c>
       <c r="M17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N17">
         <v>2.5</v>
@@ -1618,27 +1606,27 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="R17">
-        <v>32.04105090305556</v>
+        <v>15.88152983305556</v>
       </c>
       <c r="S17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:20">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18">
-        <v>13.03904891423422</v>
+        <v>6.769936468817598</v>
       </c>
       <c r="D18">
         <v>62.21893992770459</v>
@@ -1647,28 +1635,28 @@
         <v>65</v>
       </c>
       <c r="F18">
-        <v>847.5381794252241</v>
+        <v>440.0458704731439</v>
       </c>
       <c r="G18">
-        <v>12450</v>
+        <v>5400</v>
       </c>
       <c r="H18" s="2">
-        <v>45984.9375</v>
+        <v>45985.04166666666</v>
       </c>
       <c r="J18" s="2">
-        <v>45986.11621037142</v>
+        <v>45985.68485846398</v>
       </c>
       <c r="K18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L18" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1680,54 +1668,54 @@
         <v>102</v>
       </c>
       <c r="R18">
-        <v>28.28904891416667</v>
+        <v>15.43660313555556</v>
       </c>
       <c r="S18" t="s">
         <v>58</v>
       </c>
       <c r="T18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:20">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="E19">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>6950</v>
       </c>
       <c r="H19" s="2">
-        <v>45983.94791666666</v>
+        <v>45984.95833333334</v>
+      </c>
+      <c r="I19" s="2">
+        <v>45985</v>
       </c>
       <c r="J19" s="2">
-        <v>45984.25</v>
+        <v>45986.11138281981</v>
       </c>
       <c r="K19" t="s">
-        <v>42</v>
-      </c>
-      <c r="L19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -1739,15 +1727,21 @@
         <v>2</v>
       </c>
       <c r="R19">
-        <v>7.25</v>
+        <v>27.67318767555556</v>
+      </c>
+      <c r="S19" t="s">
+        <v>57</v>
+      </c>
+      <c r="T19" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:20">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <v>0.01</v>
@@ -1762,22 +1756,22 @@
         <v>0.3</v>
       </c>
       <c r="G20">
-        <v>7700</v>
+        <v>7000</v>
       </c>
       <c r="H20" s="2">
-        <v>45983.86458333334</v>
+        <v>45984.86458333334</v>
       </c>
       <c r="I20" s="2">
-        <v>45985.01041666666</v>
+        <v>45984.90625</v>
       </c>
       <c r="J20" s="2">
-        <v>45986.12741998743</v>
+        <v>45985.98400122854</v>
       </c>
       <c r="K20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N20">
         <v>1.5</v>
@@ -1786,27 +1780,27 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>11.08333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q20">
         <v>2</v>
       </c>
       <c r="R20">
-        <v>54.30807969833334</v>
+        <v>26.866029485</v>
       </c>
       <c r="S20" t="s">
         <v>57</v>
       </c>
       <c r="T20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:20">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21">
         <v>0.01</v>
@@ -1821,51 +1815,51 @@
         <v>0.3</v>
       </c>
       <c r="G21">
-        <v>6300</v>
+        <v>7500</v>
       </c>
       <c r="H21" s="2">
-        <v>45986.125</v>
+        <v>45984.78125</v>
       </c>
       <c r="I21" s="2">
-        <v>45986.625</v>
+        <v>45984.82291666666</v>
       </c>
       <c r="J21" s="2">
-        <v>45987.5085147962</v>
+        <v>45986.01578047948</v>
       </c>
       <c r="K21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>12.08333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R21">
-        <v>33.20435510888889</v>
+        <v>29.6287315075</v>
       </c>
       <c r="S21" t="s">
         <v>57</v>
       </c>
       <c r="T21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:20">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22">
         <v>0.01</v>
@@ -1880,51 +1874,51 @@
         <v>0.3</v>
       </c>
       <c r="G22">
-        <v>8100</v>
+        <v>12000</v>
       </c>
       <c r="H22" s="2">
-        <v>45986</v>
+        <v>45984.84375</v>
       </c>
       <c r="I22" s="2">
-        <v>45986.5</v>
+        <v>45984.90625</v>
       </c>
       <c r="J22" s="2">
-        <v>45987.61243112948</v>
+        <v>45986.20064948804</v>
       </c>
       <c r="K22" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N22">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>12.08333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>38.6983471075</v>
+        <v>32.56558771305556</v>
       </c>
       <c r="S22" t="s">
         <v>57</v>
       </c>
       <c r="T22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:20">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <v>0.01</v>
@@ -1939,22 +1933,22 @@
         <v>0.3</v>
       </c>
       <c r="G23">
-        <v>10050</v>
+        <v>9650</v>
       </c>
       <c r="H23" s="2">
-        <v>45984.94791666666</v>
+        <v>45989.53125</v>
       </c>
       <c r="I23" s="2">
-        <v>45985.01041666666</v>
+        <v>45989.53125</v>
       </c>
       <c r="J23" s="2">
-        <v>45986.18150670244</v>
+        <v>45990.68444318017</v>
       </c>
       <c r="K23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N23">
         <v>2</v>
@@ -1966,24 +1960,24 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="R23">
-        <v>29.60616085861111</v>
+        <v>27.67663632416667</v>
       </c>
       <c r="S23" t="s">
         <v>57</v>
       </c>
       <c r="T23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:20">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>0.01</v>
@@ -1998,22 +1992,22 @@
         <v>0.3</v>
       </c>
       <c r="G24">
-        <v>9750</v>
+        <v>11650</v>
       </c>
       <c r="H24" s="2">
-        <v>45984.92708333334</v>
+        <v>45984.9375</v>
       </c>
       <c r="I24" s="2">
-        <v>45984.98958333334</v>
+        <v>45985</v>
       </c>
       <c r="J24" s="2">
-        <v>45986.20609383736</v>
+        <v>45986.27135156703</v>
       </c>
       <c r="K24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N24">
         <v>2</v>
@@ -2028,110 +2022,113 @@
         <v>2</v>
       </c>
       <c r="R24">
-        <v>30.69625209666667</v>
+        <v>32.01243760861111</v>
       </c>
       <c r="S24" t="s">
         <v>57</v>
       </c>
       <c r="T24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:20">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25">
-        <v>0.01</v>
+        <v>9.334371213944859</v>
       </c>
       <c r="D25">
-        <v>144</v>
+        <v>62.21893992770459</v>
       </c>
       <c r="E25">
         <v>30</v>
       </c>
       <c r="F25">
-        <v>0.3</v>
+        <v>280.0311364183458</v>
       </c>
       <c r="G25">
-        <v>5600</v>
+        <v>7750</v>
       </c>
       <c r="H25" s="2">
-        <v>45986.20833333334</v>
-      </c>
-      <c r="I25" s="2">
-        <v>45986.70833333334</v>
+        <v>45983.95833333334</v>
       </c>
       <c r="J25" s="2">
-        <v>45987.47235905856</v>
+        <v>45984.84726546724</v>
       </c>
       <c r="K25" t="s">
-        <v>48</v>
+        <v>43</v>
+      </c>
+      <c r="L25" t="s">
+        <v>47</v>
       </c>
       <c r="M25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R25">
-        <v>30.33661740555556</v>
+        <v>21.33437121388889</v>
       </c>
       <c r="S25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:20">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26">
-        <v>7.559549950030005</v>
+        <v>9.110310455088765</v>
       </c>
       <c r="D26">
         <v>62.21893992770459</v>
       </c>
       <c r="E26">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F26">
-        <v>226.7864985009002</v>
+        <v>592.1701795807697</v>
       </c>
       <c r="G26">
-        <v>5600</v>
+        <v>7250</v>
       </c>
       <c r="H26" s="2">
-        <v>45984.85416666666</v>
+        <v>45984.35416666666</v>
       </c>
       <c r="J26" s="2">
-        <v>45985.45734235903</v>
+        <v>45984.83792960229</v>
       </c>
       <c r="K26" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="L26" t="s">
+        <v>47</v>
       </c>
       <c r="M26" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -2140,10 +2137,10 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R26">
-        <v>14.47621661666667</v>
+        <v>11.610310455</v>
       </c>
       <c r="S26" t="s">
         <v>58</v>
@@ -2154,43 +2151,43 @@
     </row>
     <row r="27" spans="1:20">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>10.79467394230661</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>62.21893992770459</v>
       </c>
       <c r="E27">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>323.8402182691982</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H27" s="2">
         <v>45983.95833333334</v>
       </c>
       <c r="J27" s="2">
-        <v>45984.40972222222</v>
+        <v>45984.93241696982</v>
       </c>
       <c r="K27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L27" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M27" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -2202,18 +2199,24 @@
         <v>2</v>
       </c>
       <c r="R27">
-        <v>10.83333333333333</v>
+        <v>23.37800727555555</v>
+      </c>
+      <c r="S27" t="s">
+        <v>58</v>
+      </c>
+      <c r="T27" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:20">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C28">
-        <v>10.70374352527781</v>
+        <v>11.35842716732944</v>
       </c>
       <c r="D28">
         <v>62.21893992770459</v>
@@ -2222,25 +2225,28 @@
         <v>65</v>
       </c>
       <c r="F28">
-        <v>695.7433291430575</v>
+        <v>738.2977658764135</v>
       </c>
       <c r="G28">
-        <v>10050</v>
+        <v>12350</v>
       </c>
       <c r="H28" s="2">
-        <v>45982.71908524904</v>
+        <v>45984.375</v>
       </c>
       <c r="J28" s="2">
-        <v>45983.52271345148</v>
+        <v>45985.02187890975</v>
       </c>
       <c r="K28" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="L28" t="s">
+        <v>47</v>
       </c>
       <c r="M28" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -2252,54 +2258,54 @@
         <v>2</v>
       </c>
       <c r="R28">
-        <v>19.28707685861111</v>
+        <v>15.52509383388889</v>
       </c>
       <c r="S28" t="s">
         <v>58</v>
       </c>
       <c r="T28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:20">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>9.967111735991512</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>62.21893992770459</v>
       </c>
       <c r="E29">
         <v>65</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>647.8622628394482</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="H29" s="2">
-        <v>45983.94791666666</v>
+        <v>45984.375</v>
       </c>
       <c r="J29" s="2">
-        <v>45984.39930555555</v>
+        <v>45984.92918521123</v>
       </c>
       <c r="K29" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L29" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M29" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -2311,7 +2317,13 @@
         <v>2</v>
       </c>
       <c r="R29">
-        <v>10.83333333333333</v>
+        <v>13.30044506944444</v>
+      </c>
+      <c r="S29" t="s">
+        <v>58</v>
+      </c>
+      <c r="T29" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -2319,7 +2331,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -2337,19 +2349,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2">
-        <v>45983.94791666666</v>
+        <v>45984.9375</v>
       </c>
       <c r="J30" s="2">
-        <v>45984.39930555555</v>
+        <v>45990.23958333334</v>
       </c>
       <c r="K30" t="s">
-        <v>42</v>
-      </c>
-      <c r="L30" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M30" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -2361,18 +2370,18 @@
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="R30">
-        <v>10.83333333333333</v>
+        <v>127.25</v>
       </c>
     </row>
     <row r="31" spans="1:20">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2390,10 +2399,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2">
-        <v>45985.21180555555</v>
+        <v>45983.94791666666</v>
       </c>
       <c r="J31" s="2">
-        <v>45985.36458333334</v>
+        <v>45988</v>
       </c>
       <c r="K31" t="s">
         <v>49</v>
@@ -2411,48 +2420,51 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>3.666666666666667</v>
+        <v>97.25</v>
       </c>
     </row>
     <row r="32" spans="1:20">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32">
-        <v>9.702185552813946</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>62.21893992770459</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>65</v>
       </c>
       <c r="F32">
-        <v>630.6420609329065</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>11250</v>
+        <v>0</v>
       </c>
       <c r="H32" s="2">
-        <v>45982.71908524904</v>
+        <v>45983.94791666666</v>
       </c>
       <c r="J32" s="2">
-        <v>45983.4809818693</v>
+        <v>45984.39930555555</v>
       </c>
       <c r="K32" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="L32" t="s">
+        <v>43</v>
       </c>
       <c r="M32" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -2464,54 +2476,48 @@
         <v>2</v>
       </c>
       <c r="R32">
-        <v>18.28551888611111</v>
-      </c>
-      <c r="S32" t="s">
-        <v>58</v>
-      </c>
-      <c r="T32" t="s">
-        <v>81</v>
+        <v>10.83333333333333</v>
       </c>
     </row>
     <row r="33" spans="1:20">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>40</v>
       </c>
       <c r="C33">
-        <v>11.11052498709011</v>
+        <v>0.01</v>
       </c>
       <c r="D33">
-        <v>62.21893992770459</v>
+        <v>144</v>
       </c>
       <c r="E33">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F33">
-        <v>722.1841241608569</v>
+        <v>0.3</v>
       </c>
       <c r="G33">
-        <v>11800</v>
+        <v>9550</v>
       </c>
       <c r="H33" s="2">
-        <v>45984.20833333334</v>
+        <v>45984.92708333334</v>
+      </c>
+      <c r="I33" s="2">
+        <v>45984.98958333334</v>
       </c>
       <c r="J33" s="2">
-        <v>45985.01154965225</v>
+        <v>45986.09673218481</v>
       </c>
       <c r="K33" t="s">
-        <v>50</v>
-      </c>
-      <c r="L33" t="s">
         <v>43</v>
       </c>
       <c r="M33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N33">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -2523,24 +2529,24 @@
         <v>2</v>
       </c>
       <c r="R33">
-        <v>19.27719165388889</v>
+        <v>28.07157243555556</v>
       </c>
       <c r="S33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="T33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:20">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B34" t="s">
         <v>40</v>
       </c>
       <c r="C34">
-        <v>11.71486316630421</v>
+        <v>13.03904891423422</v>
       </c>
       <c r="D34">
         <v>62.21893992770459</v>
@@ -2549,28 +2555,28 @@
         <v>65</v>
       </c>
       <c r="F34">
-        <v>761.4661058097738</v>
+        <v>847.5381794252241</v>
       </c>
       <c r="G34">
-        <v>13100</v>
+        <v>12450</v>
       </c>
       <c r="H34" s="2">
-        <v>45984.375</v>
+        <v>45984.9375</v>
       </c>
       <c r="J34" s="2">
-        <v>45985.03673040971</v>
+        <v>45986.11621037142</v>
       </c>
       <c r="K34" t="s">
         <v>43</v>
       </c>
       <c r="L34" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N34">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -2579,16 +2585,16 @@
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="R34">
-        <v>15.88152983305556</v>
+        <v>28.28904891416667</v>
       </c>
       <c r="S34" t="s">
         <v>58</v>
       </c>
       <c r="T34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -2599,37 +2605,37 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>6.769936468817598</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>62.21893992770459</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>65</v>
       </c>
       <c r="F35">
-        <v>440.0458704731439</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="H35" s="2">
-        <v>45985.04166666666</v>
+        <v>45983.94791666666</v>
       </c>
       <c r="J35" s="2">
-        <v>45985.68485846398</v>
+        <v>45984.25</v>
       </c>
       <c r="K35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L35" t="s">
         <v>43</v>
       </c>
       <c r="M35" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -2638,16 +2644,10 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="R35">
-        <v>15.43660313555556</v>
-      </c>
-      <c r="S35" t="s">
-        <v>58</v>
-      </c>
-      <c r="T35" t="s">
-        <v>84</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -2658,7 +2658,7 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>27.83720930232558</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2667,51 +2667,51 @@
         <v>30</v>
       </c>
       <c r="F36">
-        <v>835.1162790697675</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>8550</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2">
-        <v>45986.13564814815</v>
+        <v>45986.13541666666</v>
       </c>
       <c r="J36" s="2">
-        <v>45988.28835594315</v>
+        <v>45986.74539627584</v>
       </c>
       <c r="K36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L36" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M36" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q36">
         <v>2</v>
       </c>
       <c r="R36">
-        <v>51.66498708</v>
+        <v>14.63951062027778</v>
       </c>
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
         <v>41</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>21.57712765957447</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2720,51 +2720,48 @@
         <v>30</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>647.3138297872341</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>7450</v>
       </c>
       <c r="H37" s="2">
-        <v>45986.02083333334</v>
+        <v>45986.75</v>
       </c>
       <c r="J37" s="2">
-        <v>45988.91019574852</v>
+        <v>45993.0066858747</v>
       </c>
       <c r="K37" t="s">
-        <v>47</v>
-      </c>
-      <c r="L37" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M37" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>44.33333333333334</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R37">
-        <v>69.34469796444445</v>
+        <v>150.1604609927778</v>
       </c>
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
         <v>41</v>
       </c>
       <c r="C38">
-        <v>24.225</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2773,22 +2770,25 @@
         <v>30</v>
       </c>
       <c r="F38">
-        <v>726.75</v>
+        <v>665</v>
       </c>
       <c r="G38">
-        <v>7750</v>
+        <v>6450</v>
       </c>
       <c r="H38" s="2">
-        <v>45988.91666666666</v>
+        <v>45986.02106481481</v>
       </c>
       <c r="J38" s="2">
-        <v>45992.30451388889</v>
+        <v>45987.75</v>
       </c>
       <c r="K38" t="s">
-        <v>46</v>
+        <v>44</v>
+      </c>
+      <c r="L38" t="s">
+        <v>42</v>
       </c>
       <c r="M38" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="N38">
         <v>1.5</v>
@@ -2800,15 +2800,15 @@
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R38">
-        <v>81.30833333333334</v>
+        <v>41.49444444444445</v>
       </c>
     </row>
     <row r="39" spans="1:20">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
         <v>41</v>
@@ -2832,16 +2832,16 @@
         <v>45986.1875</v>
       </c>
       <c r="J39" s="2">
-        <v>45986.86311924983</v>
+        <v>45988.92418384375</v>
       </c>
       <c r="K39" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L39" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M39" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -2850,18 +2850,18 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>4</v>
+        <v>44.33333333333334</v>
       </c>
       <c r="Q39">
         <v>2</v>
       </c>
       <c r="R39">
-        <v>16.21486199583333</v>
+        <v>65.68041225</v>
       </c>
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
         <v>41</v>
@@ -2882,13 +2882,13 @@
         <v>11150</v>
       </c>
       <c r="H40" s="2">
-        <v>45986.86458333334</v>
+        <v>45988.92708333334</v>
       </c>
       <c r="J40" s="2">
-        <v>45993.25544255138</v>
+        <v>45994.33877588471</v>
       </c>
       <c r="K40" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M40" t="s">
         <v>56</v>
@@ -2906,7 +2906,7 @@
         <v>3</v>
       </c>
       <c r="R40">
-        <v>153.3806212330556</v>
+        <v>129.8806212330556</v>
       </c>
     </row>
     <row r="41" spans="1:20">
@@ -2935,16 +2935,16 @@
         <v>45986.20833333334</v>
       </c>
       <c r="J41" s="2">
-        <v>45988.92418384375</v>
+        <v>45989.33278120327</v>
       </c>
       <c r="K41" t="s">
+        <v>50</v>
+      </c>
+      <c r="L41" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" t="s">
         <v>47</v>
-      </c>
-      <c r="L41" t="s">
-        <v>47</v>
-      </c>
-      <c r="M41" t="s">
-        <v>43</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -2959,7 +2959,7 @@
         <v>2</v>
       </c>
       <c r="R41">
-        <v>65.18041225</v>
+        <v>74.98674887833333</v>
       </c>
     </row>
     <row r="42" spans="1:20">
@@ -2970,7 +2970,7 @@
         <v>41</v>
       </c>
       <c r="C42">
-        <v>28.37333333333333</v>
+        <v>24.18181818181818</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2979,25 +2979,25 @@
         <v>30</v>
       </c>
       <c r="F42">
-        <v>851.2</v>
+        <v>725.4545454545455</v>
       </c>
       <c r="G42">
-        <v>11250</v>
+        <v>10650</v>
       </c>
       <c r="H42" s="2">
-        <v>45988.92708333334</v>
+        <v>45989.33333333334</v>
       </c>
       <c r="J42" s="2">
-        <v>45994.51902777778</v>
+        <v>45992.3860479798</v>
       </c>
       <c r="K42" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M42" t="s">
         <v>56</v>
       </c>
       <c r="N42">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -3009,12 +3009,12 @@
         <v>3</v>
       </c>
       <c r="R42">
-        <v>134.2066666666667</v>
+        <v>73.26515151527778</v>
       </c>
     </row>
     <row r="43" spans="1:20">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B43" t="s">
         <v>41</v>
@@ -3035,19 +3035,19 @@
         <v>0</v>
       </c>
       <c r="H43" s="2">
-        <v>45986.09375</v>
+        <v>45986.19791666666</v>
       </c>
       <c r="J43" s="2">
-        <v>45989.04747148243</v>
+        <v>45989.04399926021</v>
       </c>
       <c r="K43" t="s">
+        <v>44</v>
+      </c>
+      <c r="L43" t="s">
+        <v>44</v>
+      </c>
+      <c r="M43" t="s">
         <v>47</v>
-      </c>
-      <c r="L43" t="s">
-        <v>47</v>
-      </c>
-      <c r="M43" t="s">
-        <v>43</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -3062,18 +3062,18 @@
         <v>2</v>
       </c>
       <c r="R43">
-        <v>70.88931557833334</v>
+        <v>68.305982245</v>
       </c>
     </row>
     <row r="44" spans="1:20">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B44" t="s">
         <v>41</v>
       </c>
       <c r="C44">
-        <v>28.44919786096257</v>
+        <v>13.02148490617351</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -3082,25 +3082,25 @@
         <v>30</v>
       </c>
       <c r="F44">
-        <v>853.475935828877</v>
+        <v>390.6445471852054</v>
       </c>
       <c r="G44">
-        <v>11300</v>
+        <v>3150</v>
       </c>
       <c r="H44" s="2">
-        <v>45986.28178104575</v>
+        <v>45989.05208333334</v>
       </c>
       <c r="J44" s="2">
-        <v>45989.82427213309</v>
+        <v>45994.08770075998</v>
       </c>
       <c r="K44" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M44" t="s">
         <v>56</v>
       </c>
       <c r="N44">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3109,21 +3109,21 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R44">
-        <v>85.0197860961111</v>
+        <v>120.8548182394444</v>
       </c>
     </row>
     <row r="45" spans="1:20">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B45" t="s">
         <v>41</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>28.22281167108753</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -3132,28 +3132,22 @@
         <v>30</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>846.6843501326259</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>11150</v>
       </c>
       <c r="H45" s="2">
-        <v>45985.45734235903</v>
-      </c>
-      <c r="I45" s="2">
-        <v>45986.75</v>
+        <v>45986.10434941521</v>
       </c>
       <c r="J45" s="2">
-        <v>45987.24604952477</v>
+        <v>45989.52317270852</v>
       </c>
       <c r="K45" t="s">
-        <v>51</v>
-      </c>
-      <c r="L45" t="s">
         <v>42</v>
       </c>
       <c r="M45" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="N45">
         <v>2.5</v>
@@ -3162,18 +3156,18 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45">
-        <v>42.92897197777778</v>
+        <v>82.05175903944445</v>
       </c>
     </row>
     <row r="46" spans="1:20">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B46" t="s">
         <v>41</v>
@@ -3185,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -3194,25 +3188,25 @@
         <v>0</v>
       </c>
       <c r="H46" s="2">
-        <v>45984.83792960229</v>
+        <v>45985.45734235903</v>
       </c>
       <c r="I46" s="2">
-        <v>45986.15625</v>
+        <v>45986.75</v>
       </c>
       <c r="J46" s="2">
-        <v>45986.46272777123</v>
+        <v>45987.24604952477</v>
       </c>
       <c r="K46" t="s">
         <v>51</v>
       </c>
       <c r="L46" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M46" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N46">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -3224,7 +3218,7 @@
         <v>1</v>
       </c>
       <c r="R46">
-        <v>38.99515605444444</v>
+        <v>42.92897197777778</v>
       </c>
     </row>
     <row r="47" spans="1:20">
@@ -3235,181 +3229,178 @@
         <v>41</v>
       </c>
       <c r="C47">
-        <v>2.448569994982438</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>65</v>
       </c>
       <c r="F47">
-        <v>159.1570496738585</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>8150</v>
+        <v>0</v>
       </c>
       <c r="H47" s="2">
-        <v>45994.44791666666</v>
+        <v>45984.83792960229</v>
       </c>
       <c r="I47" s="2">
-        <v>45994.48958333334</v>
+        <v>45986.15625</v>
       </c>
       <c r="J47" s="2">
-        <v>45994.71132930535</v>
+        <v>45986.46272777123</v>
       </c>
       <c r="K47" t="s">
-        <v>42</v>
+        <v>51</v>
+      </c>
+      <c r="L47" t="s">
+        <v>43</v>
       </c>
       <c r="M47" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="N47">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>2.448569994982438</v>
+        <v>5.25</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47">
-        <v>6.321903328333334</v>
-      </c>
-      <c r="S47" t="s">
-        <v>59</v>
-      </c>
-      <c r="T47" t="s">
-        <v>85</v>
+        <v>38.99515605444444</v>
       </c>
     </row>
     <row r="48" spans="1:20">
       <c r="A48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
         <v>41</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>2.400393507132316</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E48">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>156.0255779636006</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>7750</v>
       </c>
       <c r="H48" s="2">
-        <v>45984.93241696982</v>
+        <v>45994.27083333334</v>
       </c>
       <c r="I48" s="2">
-        <v>45986.29166666666</v>
+        <v>45994.3125</v>
       </c>
       <c r="J48" s="2">
-        <v>45986.76932273264</v>
+        <v>45994.54295894751</v>
       </c>
       <c r="K48" t="s">
-        <v>51</v>
-      </c>
-      <c r="L48" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M48" t="s">
         <v>43</v>
       </c>
       <c r="N48">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>5.25</v>
+        <v>2.400393507132316</v>
       </c>
       <c r="Q48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R48">
-        <v>44.08573830777777</v>
+        <v>6.531014740277778</v>
+      </c>
+      <c r="S48" t="s">
+        <v>59</v>
+      </c>
+      <c r="T48" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:20">
       <c r="A49" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B49" t="s">
         <v>41</v>
       </c>
       <c r="C49">
-        <v>2.840236686390533</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F49">
-        <v>184.6153846153846</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>10750</v>
+        <v>0</v>
       </c>
       <c r="H49" s="2">
-        <v>45993.16666666666</v>
+        <v>45984.93241696982</v>
       </c>
       <c r="I49" s="2">
-        <v>45993.22916666666</v>
+        <v>45986.29166666666</v>
       </c>
       <c r="J49" s="2">
-        <v>45993.49878574664</v>
+        <v>45986.76932273264</v>
       </c>
       <c r="K49" t="s">
-        <v>42</v>
+        <v>51</v>
+      </c>
+      <c r="L49" t="s">
+        <v>43</v>
       </c>
       <c r="M49" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="N49">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>2.840236686390533</v>
+        <v>5.25</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R49">
-        <v>7.970857919444445</v>
-      </c>
-      <c r="S49" t="s">
-        <v>59</v>
-      </c>
-      <c r="T49" t="s">
-        <v>86</v>
+        <v>44.08573830777777</v>
       </c>
     </row>
     <row r="50" spans="1:20">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B50" t="s">
         <v>41</v>
       </c>
       <c r="C50">
-        <v>3.415313225058004</v>
+        <v>2.892906815020862</v>
       </c>
       <c r="D50">
         <v>16</v>
@@ -3418,57 +3409,57 @@
         <v>65</v>
       </c>
       <c r="F50">
-        <v>221.9953596287703</v>
+        <v>188.0389429763561</v>
       </c>
       <c r="G50">
-        <v>12850</v>
+        <v>11150</v>
       </c>
       <c r="H50" s="2">
-        <v>45989.71875</v>
+        <v>45994.25</v>
       </c>
       <c r="I50" s="2">
-        <v>45989.80208333334</v>
+        <v>45994.3125</v>
       </c>
       <c r="J50" s="2">
-        <v>45990.15272138437</v>
+        <v>45994.57192667285</v>
       </c>
       <c r="K50" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M50" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>3.415313225058004</v>
+        <v>2.892906815020862</v>
       </c>
       <c r="Q50">
         <v>2</v>
       </c>
       <c r="R50">
-        <v>10.415313225</v>
+        <v>7.726240148333333</v>
       </c>
       <c r="S50" t="s">
         <v>59</v>
       </c>
       <c r="T50" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:20">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
         <v>41</v>
       </c>
       <c r="C51">
-        <v>2.909090909090909</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="D51">
         <v>16</v>
@@ -3477,46 +3468,46 @@
         <v>65</v>
       </c>
       <c r="F51">
-        <v>189.0909090909091</v>
+        <v>226.7298578199052</v>
       </c>
       <c r="G51">
-        <v>12250</v>
+        <v>13300</v>
       </c>
       <c r="H51" s="2">
-        <v>45992.20833333334</v>
+        <v>45989.41666666666</v>
       </c>
       <c r="I51" s="2">
-        <v>45992.28125</v>
+        <v>45989.5</v>
       </c>
       <c r="J51" s="2">
-        <v>45992.57607323233</v>
+        <v>45989.85367298579</v>
       </c>
       <c r="K51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N51">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>2.909090909090909</v>
+        <v>3.488151658767772</v>
       </c>
       <c r="Q51">
         <v>2</v>
       </c>
       <c r="R51">
-        <v>8.825757575833334</v>
+        <v>10.48815165888889</v>
       </c>
       <c r="S51" t="s">
         <v>59</v>
       </c>
       <c r="T51" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:20">
@@ -3527,7 +3518,7 @@
         <v>41</v>
       </c>
       <c r="C52">
-        <v>1.921787709497207</v>
+        <v>2.885771543086173</v>
       </c>
       <c r="D52">
         <v>16</v>
@@ -3536,45 +3527,104 @@
         <v>65</v>
       </c>
       <c r="F52">
-        <v>124.9162011173184</v>
+        <v>187.5751503006012</v>
       </c>
       <c r="G52">
-        <v>6000</v>
+        <v>12050</v>
       </c>
       <c r="H52" s="2">
-        <v>45994.44791666666</v>
+        <v>45992.29166666666</v>
       </c>
       <c r="I52" s="2">
-        <v>45994.48958333334</v>
+        <v>45992.36521464647</v>
       </c>
       <c r="J52" s="2">
-        <v>45994.70326893234</v>
+        <v>45992.65906623854</v>
       </c>
       <c r="K52" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M52" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N52">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>1.921787709497207</v>
+        <v>2.885771543086173</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
       <c r="R52">
-        <v>6.128454376111111</v>
+        <v>8.817589724999999</v>
       </c>
       <c r="S52" t="s">
         <v>59</v>
       </c>
       <c r="T52" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20">
+      <c r="A53" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53">
+        <v>1.756862745098039</v>
+      </c>
+      <c r="D53">
+        <v>16</v>
+      </c>
+      <c r="E53">
+        <v>65</v>
+      </c>
+      <c r="F53">
+        <v>114.1960784313725</v>
+      </c>
+      <c r="G53">
+        <v>5750</v>
+      </c>
+      <c r="H53" s="2">
+        <v>45994.28125</v>
+      </c>
+      <c r="I53" s="2">
+        <v>45994.3125</v>
+      </c>
+      <c r="J53" s="2">
+        <v>45994.46753405464</v>
+      </c>
+      <c r="K53" t="s">
+        <v>43</v>
+      </c>
+      <c r="M53" t="s">
+        <v>43</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>1.756862745098039</v>
+      </c>
+      <c r="Q53">
+        <v>2</v>
+      </c>
+      <c r="R53">
+        <v>4.470817311388889</v>
+      </c>
+      <c r="S53" t="s">
+        <v>59</v>
+      </c>
+      <c r="T53" t="s">
         <v>89</v>
       </c>
     </row>
